--- a/samples/06_위험률표_종신_남녀.xlsx
+++ b/samples/06_위험률표_종신_남녀.xlsx
@@ -459,16 +459,16 @@
         <v>40</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00086</v>
+        <v>0.0008999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00051</v>
+        <v>0.0005067</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000147</v>
+        <v>0.000144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000167</v>
+        <v>0.00017495</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         <v>41</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00094</v>
+        <v>0.0009773</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00056</v>
+        <v>0.0005637</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000159</v>
+        <v>0.00015683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000187</v>
+        <v>0.00019545</v>
       </c>
     </row>
     <row r="4">
@@ -493,16 +493,16 @@
         <v>42</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00105</v>
+        <v>0.00108</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00061</v>
+        <v>0.0006202</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000171</v>
+        <v>0.00017003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000209</v>
+        <v>0.00021695</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +510,16 @@
         <v>43</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00118</v>
+        <v>0.001197</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00067</v>
+        <v>0.0006849</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000186</v>
+        <v>0.00018623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000231</v>
+        <v>0.00023725</v>
       </c>
     </row>
     <row r="6">
@@ -527,16 +527,16 @@
         <v>44</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00134</v>
+        <v>0.001339</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00072</v>
+        <v>0.0007364</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000204</v>
+        <v>0.00020543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000255</v>
+        <v>0.00025855</v>
       </c>
     </row>
     <row r="7">
@@ -544,16 +544,16 @@
         <v>45</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00152</v>
+        <v>0.001498</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00078</v>
+        <v>0.0007943</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000229</v>
+        <v>0.00023113</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000286</v>
+        <v>0.00028625</v>
       </c>
     </row>
     <row r="8">
@@ -561,16 +561,16 @@
         <v>46</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0017</v>
+        <v>0.001658</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00084</v>
+        <v>0.0008485</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000259</v>
+        <v>0.00026093</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000321</v>
+        <v>0.00031775</v>
       </c>
     </row>
     <row r="9">
@@ -578,16 +578,16 @@
         <v>47</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00188</v>
+        <v>0.001823</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00091</v>
+        <v>0.0009097</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000294</v>
+        <v>0.00029463</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000361</v>
+        <v>0.00035455</v>
       </c>
     </row>
     <row r="10">
@@ -595,16 +595,16 @@
         <v>48</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00206</v>
+        <v>0.001997</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009700000000000001</v>
+        <v>0.0009596</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000329</v>
+        <v>0.00032673</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000401</v>
+        <v>0.00039265</v>
       </c>
     </row>
     <row r="11">
@@ -612,16 +612,16 @@
         <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00225</v>
+        <v>0.002192</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00104</v>
+        <v>0.00102</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000367</v>
+        <v>0.00036063</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00044</v>
+        <v>0.00043165</v>
       </c>
     </row>
     <row r="12">
@@ -629,16 +629,16 @@
         <v>50</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00244</v>
+        <v>0.002398</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00111</v>
+        <v>0.001084</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00026</v>
+        <v>0.0002524</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000372</v>
+        <v>0.00036632</v>
       </c>
     </row>
     <row r="13">
@@ -646,16 +646,16 @@
         <v>51</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00265</v>
+        <v>0.002633</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00118</v>
+        <v>0.001152</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000281</v>
+        <v>0.0002706</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000399</v>
+        <v>0.00039642</v>
       </c>
     </row>
     <row r="14">
@@ -663,16 +663,16 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0029</v>
+        <v>0.002912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00126</v>
+        <v>0.001237</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000302</v>
+        <v>0.0002896</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000427</v>
+        <v>0.00042852</v>
       </c>
     </row>
     <row r="15">
@@ -680,16 +680,16 @@
         <v>53</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00317</v>
+        <v>0.00321</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00134</v>
+        <v>0.001329</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000323</v>
+        <v>0.0003097</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000461</v>
+        <v>0.00046682</v>
       </c>
     </row>
     <row r="16">
@@ -697,16 +697,16 @@
         <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00348</v>
+        <v>0.003541</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00142</v>
+        <v>0.001427</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000342</v>
+        <v>0.0003295</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000511</v>
+        <v>0.00052062</v>
       </c>
     </row>
     <row r="17">
@@ -714,16 +714,16 @@
         <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00381</v>
+        <v>0.003876</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00151</v>
+        <v>0.001539</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000359</v>
+        <v>0.0003491</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000584</v>
+        <v>0.00059622</v>
       </c>
     </row>
     <row r="18">
@@ -731,16 +731,16 @@
         <v>56</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00419</v>
+        <v>0.004241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00161</v>
+        <v>0.001662</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000375</v>
+        <v>0.0003691</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00068</v>
+        <v>0.00069242</v>
       </c>
     </row>
     <row r="19">
@@ -748,16 +748,16 @@
         <v>57</v>
       </c>
       <c r="B19" t="n">
-        <v>0.00463</v>
+        <v>0.004643</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00174</v>
+        <v>0.001815</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000389</v>
+        <v>0.0003879</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000792</v>
+        <v>0.00080052</v>
       </c>
     </row>
     <row r="20">
@@ -765,16 +765,16 @@
         <v>58</v>
       </c>
       <c r="B20" t="n">
-        <v>0.00514</v>
+        <v>0.00509</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00188</v>
+        <v>0.001972</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000402</v>
+        <v>0.0004059</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0009120000000000001</v>
+        <v>0.00091152</v>
       </c>
     </row>
     <row r="21">
@@ -782,16 +782,16 @@
         <v>59</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00571</v>
+        <v>0.005578</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00205</v>
+        <v>0.002151</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000417</v>
+        <v>0.0004253</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001032</v>
+        <v>0.00101762</v>
       </c>
     </row>
     <row r="22">
@@ -799,16 +799,16 @@
         <v>60</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00633</v>
+        <v>0.006106</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00223</v>
+        <v>0.002329</v>
       </c>
       <c r="D22" t="n">
-        <v>0.000517</v>
+        <v>0.0005356</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000924</v>
+        <v>0.0009007</v>
       </c>
     </row>
     <row r="23">
@@ -816,16 +816,16 @@
         <v>61</v>
       </c>
       <c r="B23" t="n">
-        <v>0.007</v>
+        <v>0.006689</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00244</v>
+        <v>0.002524</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000531</v>
+        <v>0.0005508000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001013</v>
+        <v>0.0009762</v>
       </c>
     </row>
     <row r="24">
@@ -833,16 +833,16 @@
         <v>62</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00772</v>
+        <v>0.007343</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00269</v>
+        <v>0.002748</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000544</v>
+        <v>0.0005627</v>
       </c>
       <c r="E24" t="n">
-        <v>0.001101</v>
+        <v>0.0010527</v>
       </c>
     </row>
     <row r="25">
@@ -850,16 +850,16 @@
         <v>63</v>
       </c>
       <c r="B25" t="n">
-        <v>0.00848</v>
+        <v>0.008076</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00297</v>
+        <v>0.002993</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000562</v>
+        <v>0.0005777</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00119</v>
+        <v>0.0011345</v>
       </c>
     </row>
     <row r="26">
@@ -867,16 +867,16 @@
         <v>64</v>
       </c>
       <c r="B26" t="n">
-        <v>0.00928</v>
+        <v>0.008899000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00327</v>
+        <v>0.003253</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00059</v>
+        <v>0.0006013</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001278</v>
+        <v>0.0012215</v>
       </c>
     </row>
     <row r="27">
@@ -884,16 +884,16 @@
         <v>65</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01015</v>
+        <v>0.009845</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00362</v>
+        <v>0.003566</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000629</v>
+        <v>0.0006349</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001365</v>
+        <v>0.0013155</v>
       </c>
     </row>
     <row r="28">
@@ -901,16 +901,16 @@
         <v>66</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01116</v>
+        <v>0.01098</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00404</v>
+        <v>0.003959</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000681</v>
+        <v>0.0006814</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001449</v>
+        <v>0.0014125</v>
       </c>
     </row>
     <row r="29">
@@ -918,16 +918,16 @@
         <v>67</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0124</v>
+        <v>0.01238</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00458</v>
+        <v>0.004487</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00074</v>
+        <v>0.0007359000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001533</v>
+        <v>0.0015145</v>
       </c>
     </row>
     <row r="30">
@@ -935,16 +935,16 @@
         <v>68</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01391</v>
+        <v>0.01408</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00524</v>
+        <v>0.005158</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0008050000000000001</v>
+        <v>0.0007987</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001617</v>
+        <v>0.0016185</v>
       </c>
     </row>
     <row r="31">
@@ -952,16 +952,16 @@
         <v>69</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01565</v>
+        <v>0.016</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00601</v>
+        <v>0.005966</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00087</v>
+        <v>0.0008651</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001702</v>
+        <v>0.0017225</v>
       </c>
     </row>
     <row r="32">
@@ -969,16 +969,16 @@
         <v>70</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01751</v>
+        <v>0.01799</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00687</v>
+        <v>0.006892</v>
       </c>
       <c r="D32" t="n">
-        <v>0.001048</v>
+        <v>0.001045</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001846</v>
+        <v>0.0018806</v>
       </c>
     </row>
     <row r="33">
@@ -986,16 +986,16 @@
         <v>71</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01937</v>
+        <v>0.0199</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.007927</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001111</v>
+        <v>0.0011176</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001926</v>
+        <v>0.0019666</v>
       </c>
     </row>
     <row r="34">
@@ -1003,16 +1003,16 @@
         <v>72</v>
       </c>
       <c r="B34" t="n">
-        <v>0.02111</v>
+        <v>0.02159</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008880000000000001</v>
+        <v>0.009075</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001175</v>
+        <v>0.0011943</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002008</v>
+        <v>0.0020456</v>
       </c>
     </row>
     <row r="35">
@@ -1020,16 +1020,16 @@
         <v>73</v>
       </c>
       <c r="B35" t="n">
-        <v>0.02265</v>
+        <v>0.02297</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01008</v>
+        <v>0.01035</v>
       </c>
       <c r="D35" t="n">
-        <v>0.001237</v>
+        <v>0.0012697</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002096</v>
+        <v>0.0021216</v>
       </c>
     </row>
     <row r="36">
@@ -1037,16 +1037,16 @@
         <v>74</v>
       </c>
       <c r="B36" t="n">
-        <v>0.02402</v>
+        <v>0.02411</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01139</v>
+        <v>0.01169</v>
       </c>
       <c r="D36" t="n">
-        <v>0.001294</v>
+        <v>0.0013387</v>
       </c>
       <c r="E36" t="n">
-        <v>0.002205</v>
+        <v>0.0022116</v>
       </c>
     </row>
     <row r="37">
@@ -1054,16 +1054,16 @@
         <v>75</v>
       </c>
       <c r="B37" t="n">
-        <v>0.02546</v>
+        <v>0.02529</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01278</v>
+        <v>0.01304</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001347</v>
+        <v>0.0013997</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002338</v>
+        <v>0.0023216</v>
       </c>
     </row>
     <row r="38">
@@ -1071,16 +1071,16 @@
         <v>76</v>
       </c>
       <c r="B38" t="n">
-        <v>0.02735</v>
+        <v>0.02694</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01423</v>
+        <v>0.01438</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001393</v>
+        <v>0.0014477</v>
       </c>
       <c r="E38" t="n">
-        <v>0.002497</v>
+        <v>0.0024566</v>
       </c>
     </row>
     <row r="39">
@@ -1088,16 +1088,16 @@
         <v>77</v>
       </c>
       <c r="B39" t="n">
-        <v>0.03001</v>
+        <v>0.02942</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01573</v>
+        <v>0.01568</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001437</v>
+        <v>0.0014877</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002674</v>
+        <v>0.0026146</v>
       </c>
     </row>
     <row r="40">
@@ -1105,16 +1105,16 @@
         <v>78</v>
       </c>
       <c r="B40" t="n">
-        <v>0.03347</v>
+        <v>0.03283</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01717</v>
+        <v>0.01687</v>
       </c>
       <c r="D40" t="n">
-        <v>0.001478</v>
+        <v>0.0015167</v>
       </c>
       <c r="E40" t="n">
-        <v>0.002863</v>
+        <v>0.0027946</v>
       </c>
     </row>
     <row r="41">
@@ -1122,16 +1122,16 @@
         <v>79</v>
       </c>
       <c r="B41" t="n">
-        <v>0.03759</v>
+        <v>0.03708</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01856</v>
+        <v>0.01798</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001519</v>
+        <v>0.0015407</v>
       </c>
       <c r="E41" t="n">
-        <v>0.003048</v>
+        <v>0.0029846</v>
       </c>
     </row>
     <row r="42">
@@ -1139,16 +1139,16 @@
         <v>80</v>
       </c>
       <c r="B42" t="n">
-        <v>0.04231</v>
+        <v>0.04215</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02013</v>
+        <v>0.01928</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00157</v>
+        <v>0.0015626</v>
       </c>
       <c r="E42" t="n">
-        <v>0.003313</v>
+        <v>0.0032617</v>
       </c>
     </row>
     <row r="43">
@@ -1156,16 +1156,16 @@
         <v>81</v>
       </c>
       <c r="B43" t="n">
-        <v>0.04771</v>
+        <v>0.04814</v>
       </c>
       <c r="C43" t="n">
-        <v>0.02226</v>
+        <v>0.02118</v>
       </c>
       <c r="D43" t="n">
-        <v>0.001601</v>
+        <v>0.0015736</v>
       </c>
       <c r="E43" t="n">
-        <v>0.003478</v>
+        <v>0.0034637</v>
       </c>
     </row>
     <row r="44">
@@ -1173,16 +1173,16 @@
         <v>82</v>
       </c>
       <c r="B44" t="n">
-        <v>0.05396</v>
+        <v>0.05519</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0253</v>
+        <v>0.02406</v>
       </c>
       <c r="D44" t="n">
-        <v>0.001637</v>
+        <v>0.0015936</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00365</v>
+        <v>0.0036837</v>
       </c>
     </row>
     <row r="45">
@@ -1190,16 +1190,16 @@
         <v>83</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0611</v>
+        <v>0.06326</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02927</v>
+        <v>0.02798</v>
       </c>
       <c r="D45" t="n">
-        <v>0.001697</v>
+        <v>0.0016416</v>
       </c>
       <c r="E45" t="n">
-        <v>0.003867</v>
+        <v>0.0039557</v>
       </c>
     </row>
     <row r="46">
@@ -1207,16 +1207,16 @@
         <v>84</v>
       </c>
       <c r="B46" t="n">
-        <v>0.06905</v>
+        <v>0.07214</v>
       </c>
       <c r="C46" t="n">
-        <v>0.03405</v>
+        <v>0.03287</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001805</v>
+        <v>0.0017446</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004169</v>
+        <v>0.0043127</v>
       </c>
     </row>
     <row r="47">
@@ -1224,16 +1224,16 @@
         <v>85</v>
       </c>
       <c r="B47" t="n">
-        <v>0.07772999999999999</v>
+        <v>0.08157</v>
       </c>
       <c r="C47" t="n">
-        <v>0.03953</v>
+        <v>0.03865</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00198</v>
+        <v>0.0019196</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00458</v>
+        <v>0.0047747</v>
       </c>
     </row>
     <row r="48">
@@ -1241,16 +1241,16 @@
         <v>86</v>
       </c>
       <c r="B48" t="n">
-        <v>0.08722000000000001</v>
+        <v>0.09145</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04583</v>
+        <v>0.04543</v>
       </c>
       <c r="D48" t="n">
-        <v>0.002224</v>
+        <v>0.0021716</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005104</v>
+        <v>0.0053377</v>
       </c>
     </row>
     <row r="49">
@@ -1258,16 +1258,16 @@
         <v>87</v>
       </c>
       <c r="B49" t="n">
-        <v>0.09773999999999999</v>
+        <v>0.1019</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05316</v>
+        <v>0.05336</v>
       </c>
       <c r="D49" t="n">
-        <v>0.002533</v>
+        <v>0.0024976</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00572</v>
+        <v>0.0059687</v>
       </c>
     </row>
     <row r="50">
@@ -1275,16 +1275,16 @@
         <v>88</v>
       </c>
       <c r="B50" t="n">
-        <v>0.10926</v>
+        <v>0.1127</v>
       </c>
       <c r="C50" t="n">
-        <v>0.06147</v>
+        <v>0.06228</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002891</v>
+        <v>0.0028806</v>
       </c>
       <c r="E50" t="n">
-        <v>0.006391</v>
+        <v>0.0066227</v>
       </c>
     </row>
     <row r="51">
@@ -1292,16 +1292,16 @@
         <v>89</v>
       </c>
       <c r="B51" t="n">
-        <v>0.12171</v>
+        <v>0.1239</v>
       </c>
       <c r="C51" t="n">
-        <v>0.07069</v>
+        <v>0.07198</v>
       </c>
       <c r="D51" t="n">
-        <v>0.003283</v>
+        <v>0.0033016</v>
       </c>
       <c r="E51" t="n">
-        <v>0.007088</v>
+        <v>0.0072667</v>
       </c>
     </row>
     <row r="52">
@@ -1309,16 +1309,16 @@
         <v>90</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1351</v>
+        <v>0.1355</v>
       </c>
       <c r="C52" t="n">
-        <v>0.08087999999999999</v>
+        <v>0.08235000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>0.003702</v>
+        <v>0.0037456</v>
       </c>
       <c r="E52" t="n">
-        <v>0.007803</v>
+        <v>0.007897700000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1326,16 +1326,16 @@
         <v>91</v>
       </c>
       <c r="B53" t="n">
-        <v>0.14969</v>
+        <v>0.1482</v>
       </c>
       <c r="C53" t="n">
-        <v>0.09243999999999999</v>
+        <v>0.09365999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>0.004139</v>
+        <v>0.0041946</v>
       </c>
       <c r="E53" t="n">
-        <v>0.008531</v>
+        <v>0.0085247</v>
       </c>
     </row>
     <row r="54">
@@ -1343,16 +1343,16 @@
         <v>92</v>
       </c>
       <c r="B54" t="n">
-        <v>0.16591</v>
+        <v>0.1626</v>
       </c>
       <c r="C54" t="n">
-        <v>0.10591</v>
+        <v>0.1064</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00458</v>
+        <v>0.0046276</v>
       </c>
       <c r="E54" t="n">
-        <v>0.009266999999999999</v>
+        <v>0.009160700000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1360,16 +1360,16 @@
         <v>93</v>
       </c>
       <c r="B55" t="n">
-        <v>0.18379</v>
+        <v>0.1792</v>
       </c>
       <c r="C55" t="n">
-        <v>0.12144</v>
+        <v>0.1207</v>
       </c>
       <c r="D55" t="n">
-        <v>0.005006</v>
+        <v>0.0050206</v>
       </c>
       <c r="E55" t="n">
-        <v>0.010007</v>
+        <v>0.009823699999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1377,16 +1377,16 @@
         <v>94</v>
       </c>
       <c r="B56" t="n">
-        <v>0.20317</v>
+        <v>0.1981</v>
       </c>
       <c r="C56" t="n">
-        <v>0.13884</v>
+        <v>0.1365</v>
       </c>
       <c r="D56" t="n">
-        <v>0.005402</v>
+        <v>0.0053586</v>
       </c>
       <c r="E56" t="n">
-        <v>0.010744</v>
+        <v>0.0105277</v>
       </c>
     </row>
     <row r="57">
@@ -1394,16 +1394,16 @@
         <v>95</v>
       </c>
       <c r="B57" t="n">
-        <v>0.22392</v>
+        <v>0.2194</v>
       </c>
       <c r="C57" t="n">
-        <v>0.15766</v>
+        <v>0.1537</v>
       </c>
       <c r="D57" t="n">
-        <v>0.005759</v>
+        <v>0.0056406</v>
       </c>
       <c r="E57" t="n">
-        <v>0.011471</v>
+        <v>0.0112677</v>
       </c>
     </row>
     <row r="58">
@@ -1411,16 +1411,16 @@
         <v>96</v>
       </c>
       <c r="B58" t="n">
-        <v>0.24623</v>
+        <v>0.2434</v>
       </c>
       <c r="C58" t="n">
-        <v>0.17764</v>
+        <v>0.1724</v>
       </c>
       <c r="D58" t="n">
-        <v>0.006077</v>
+        <v>0.0058796</v>
       </c>
       <c r="E58" t="n">
-        <v>0.012169</v>
+        <v>0.0120377</v>
       </c>
     </row>
     <row r="59">
@@ -1428,16 +1428,16 @@
         <v>97</v>
       </c>
       <c r="B59" t="n">
-        <v>0.27053</v>
+        <v>0.2703</v>
       </c>
       <c r="C59" t="n">
-        <v>0.19884</v>
+        <v>0.1931</v>
       </c>
       <c r="D59" t="n">
-        <v>0.006363</v>
+        <v>0.0060956</v>
       </c>
       <c r="E59" t="n">
-        <v>0.012824</v>
+        <v>0.0128177</v>
       </c>
     </row>
     <row r="60">
@@ -1445,16 +1445,16 @@
         <v>98</v>
       </c>
       <c r="B60" t="n">
-        <v>0.29699</v>
+        <v>0.2998</v>
       </c>
       <c r="C60" t="n">
-        <v>0.22137</v>
+        <v>0.2163</v>
       </c>
       <c r="D60" t="n">
-        <v>0.006638</v>
+        <v>0.0063236</v>
       </c>
       <c r="E60" t="n">
-        <v>0.013428</v>
+        <v>0.0135577</v>
       </c>
     </row>
     <row r="61">
@@ -1462,16 +1462,16 @@
         <v>99</v>
       </c>
       <c r="B61" t="n">
-        <v>0.32546</v>
+        <v>0.3312</v>
       </c>
       <c r="C61" t="n">
-        <v>0.24524</v>
+        <v>0.2421</v>
       </c>
       <c r="D61" t="n">
-        <v>0.006914</v>
+        <v>0.0065856</v>
       </c>
       <c r="E61" t="n">
-        <v>0.013992</v>
+        <v>0.0142577</v>
       </c>
     </row>
     <row r="62">
@@ -1479,16 +1479,16 @@
         <v>100</v>
       </c>
       <c r="B62" t="n">
-        <v>0.35547</v>
+        <v>0.3632</v>
       </c>
       <c r="C62" t="n">
-        <v>0.27011</v>
+        <v>0.2704</v>
       </c>
       <c r="D62" t="n">
-        <v>0.007205</v>
+        <v>0.0069006</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01454</v>
+        <v>0.0149077</v>
       </c>
     </row>
     <row r="63">
@@ -1496,16 +1496,16 @@
         <v>101</v>
       </c>
       <c r="B63" t="n">
-        <v>0.38675</v>
+        <v>0.3949</v>
       </c>
       <c r="C63" t="n">
-        <v>0.29573</v>
+        <v>0.3004</v>
       </c>
       <c r="D63" t="n">
-        <v>0.007513</v>
+        <v>0.0072696</v>
       </c>
       <c r="E63" t="n">
-        <v>0.015111</v>
+        <v>0.0155177</v>
       </c>
     </row>
     <row r="64">
@@ -1513,16 +1513,16 @@
         <v>102</v>
       </c>
       <c r="B64" t="n">
-        <v>0.41937</v>
+        <v>0.4258</v>
       </c>
       <c r="C64" t="n">
-        <v>0.32211</v>
+        <v>0.3317</v>
       </c>
       <c r="D64" t="n">
-        <v>0.007833</v>
+        <v>0.0076826</v>
       </c>
       <c r="E64" t="n">
-        <v>0.015733</v>
+        <v>0.0160977</v>
       </c>
     </row>
     <row r="65">
@@ -1530,16 +1530,16 @@
         <v>103</v>
       </c>
       <c r="B65" t="n">
-        <v>0.4509</v>
+        <v>0.4533</v>
       </c>
       <c r="C65" t="n">
-        <v>0.34718</v>
+        <v>0.3614</v>
       </c>
       <c r="D65" t="n">
-        <v>0.008159</v>
+        <v>0.0081206</v>
       </c>
       <c r="E65" t="n">
-        <v>0.016423</v>
+        <v>0.0166677</v>
       </c>
     </row>
     <row r="66">
@@ -1547,16 +1547,16 @@
         <v>104</v>
       </c>
       <c r="B66" t="n">
-        <v>0.48142</v>
+        <v>0.4776</v>
       </c>
       <c r="C66" t="n">
-        <v>0.37107</v>
+        <v>0.3886</v>
       </c>
       <c r="D66" t="n">
-        <v>0.008640999999999999</v>
+        <v>0.008719599999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>0.017182</v>
+        <v>0.0172377</v>
       </c>
     </row>
     <row r="67">
@@ -1564,16 +1564,16 @@
         <v>105</v>
       </c>
       <c r="B67" t="n">
-        <v>0.5438</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3983</v>
+        <v>0.4175</v>
       </c>
       <c r="D67" t="n">
-        <v>0.009152</v>
+        <v>0.009335599999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>0.017997</v>
+        <v>0.0177977</v>
       </c>
     </row>
     <row r="68">
@@ -1581,16 +1581,16 @@
         <v>106</v>
       </c>
       <c r="B68" t="n">
-        <v>0.61426</v>
+        <v>0.5928</v>
       </c>
       <c r="C68" t="n">
-        <v>0.43677</v>
+        <v>0.4559</v>
       </c>
       <c r="D68" t="n">
-        <v>0.009695</v>
+        <v>0.009954599999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>0.018844</v>
+        <v>0.0183577</v>
       </c>
     </row>
     <row r="69">
@@ -1598,16 +1598,16 @@
         <v>107</v>
       </c>
       <c r="B69" t="n">
-        <v>0.69385</v>
+        <v>0.6629</v>
       </c>
       <c r="C69" t="n">
-        <v>0.50143</v>
+        <v>0.5188</v>
       </c>
       <c r="D69" t="n">
-        <v>0.01027</v>
+        <v>0.0105636</v>
       </c>
       <c r="E69" t="n">
-        <v>0.019707</v>
+        <v>0.0189677</v>
       </c>
     </row>
     <row r="70">
@@ -1615,16 +1615,16 @@
         <v>108</v>
       </c>
       <c r="B70" t="n">
-        <v>0.7837499999999999</v>
+        <v>0.7449</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5756599999999999</v>
+        <v>0.5885</v>
       </c>
       <c r="D70" t="n">
-        <v>0.01088</v>
+        <v>0.0111536</v>
       </c>
       <c r="E70" t="n">
-        <v>0.020574</v>
+        <v>0.0196277</v>
       </c>
     </row>
     <row r="71">
@@ -1632,16 +1632,16 @@
         <v>109</v>
       </c>
       <c r="B71" t="n">
-        <v>0.8853</v>
+        <v>0.8419</v>
       </c>
       <c r="C71" t="n">
-        <v>0.66088</v>
+        <v>0.6669</v>
       </c>
       <c r="D71" t="n">
-        <v>0.011528</v>
+        <v>0.0117336</v>
       </c>
       <c r="E71" t="n">
-        <v>0.021442</v>
+        <v>0.0203877</v>
       </c>
     </row>
     <row r="72">
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0.75872</v>
+        <v>0.7565</v>
       </c>
       <c r="D72" t="n">
-        <v>0.011528</v>
+        <v>0.0117336</v>
       </c>
       <c r="E72" t="n">
-        <v>0.022563</v>
+        <v>0.0215177</v>
       </c>
     </row>
   </sheetData>
